--- a/artfynd/S 7176-2022 artfynd.xlsx
+++ b/artfynd/S 7176-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89377935</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89378159</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/538903</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74624388</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/640842</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,6 +1379,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/640846</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1461,6 +1496,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/614026</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/705151</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1688,6 +1733,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/875556</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1800,6 +1850,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/725249</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1020179</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2015,6 +2075,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2076316</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2121,6 +2186,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88657073</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2233,6 +2303,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2072873</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2340,6 +2415,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13223641</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2450,6 +2530,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119799</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2560,6 +2645,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119802</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2670,6 +2760,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119804</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2780,6 +2875,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119806</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2890,6 +2990,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119807</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3005,6 +3110,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119808</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3115,6 +3225,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119980</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3225,6 +3340,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119981</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3340,6 +3460,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120057</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3450,6 +3575,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120059</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3560,6 +3690,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120061</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3670,6 +3805,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120066</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3780,6 +3920,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120067</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3882,6 +4027,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3784371</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3984,6 +4134,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3784372</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4094,6 +4249,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106018495</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4204,6 +4364,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120982</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4314,6 +4479,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120983</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4424,6 +4594,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120985</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4534,6 +4709,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106120986</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4644,6 +4824,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121012</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4754,6 +4939,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121013</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4864,6 +5054,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121014</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4974,6 +5169,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121015</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5084,6 +5284,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121016</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5194,6 +5399,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121017</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5304,8 +5514,57 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121018</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>